--- a/olive_FMBN/data/extra_metadata_F.xlsx
+++ b/olive_FMBN/data/extra_metadata_F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenioparente/Library/CloudStorage/GoogleDrive-eugenio.parente@unibas.it/Shared drives/METAolive_Unibas/sviluppo_Metaolive_FMBN/olive_FMBN_250226/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenio/Dropbox/GitHub_repos/Metaolive/olive_FMBN/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C11C7ED5-3D38-C046-833D-C8EA63A3F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E28F9C-4DA4-144F-9369-2F6BF5F11C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5740" yWindow="3620" windowWidth="39020" windowHeight="20520" xr2:uid="{3BB29AE4-6057-5440-85FA-A00BE67DD871}"/>
+    <workbookView xWindow="0" yWindow="1080" windowWidth="38400" windowHeight="20520" xr2:uid="{3BB29AE4-6057-5440-85FA-A00BE67DD871}"/>
   </bookViews>
   <sheets>
     <sheet name="extra_metadata_F" sheetId="1" r:id="rId1"/>
@@ -9405,48 +9405,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Calcolo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Cella collegata" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Cella da controllare" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Colore 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Colore 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Colore 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Colore 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Colore 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Colore 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Neutrale" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Testo avviso" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Testo descrittivo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Titolo" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Titolo 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Titolo 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Titolo 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Titolo 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Totale" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9462,9 +9462,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9502,7 +9502,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9608,7 +9608,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9750,7 +9750,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -40089,14 +40089,14 @@
         <v>1278</v>
       </c>
       <c r="V389" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W389" t="s">
         <v>109</v>
       </c>
       <c r="X389" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y389" t="s">
         <v>72</v>
@@ -40167,14 +40167,14 @@
         <v>1278</v>
       </c>
       <c r="V390" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W390" t="s">
         <v>109</v>
       </c>
       <c r="X390" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y390" t="s">
         <v>72</v>
@@ -40245,14 +40245,14 @@
         <v>1278</v>
       </c>
       <c r="V391" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W391" t="s">
         <v>109</v>
       </c>
       <c r="X391" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y391" t="s">
         <v>72</v>
@@ -40323,14 +40323,14 @@
         <v>1278</v>
       </c>
       <c r="V392" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W392" t="s">
         <v>109</v>
       </c>
       <c r="X392" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y392" t="s">
         <v>72</v>
@@ -40401,14 +40401,14 @@
         <v>1278</v>
       </c>
       <c r="V393" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W393" t="s">
         <v>109</v>
       </c>
       <c r="X393" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y393" t="s">
         <v>72</v>
@@ -40479,14 +40479,14 @@
         <v>1278</v>
       </c>
       <c r="V394" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W394" t="s">
         <v>109</v>
       </c>
       <c r="X394" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y394" t="s">
         <v>72</v>
@@ -40557,14 +40557,14 @@
         <v>1278</v>
       </c>
       <c r="V395" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W395" t="s">
         <v>109</v>
       </c>
       <c r="X395" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y395" t="s">
         <v>72</v>
@@ -40635,14 +40635,14 @@
         <v>1278</v>
       </c>
       <c r="V396" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W396" t="s">
         <v>109</v>
       </c>
       <c r="X396" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y396" t="s">
         <v>72</v>
@@ -40713,14 +40713,14 @@
         <v>1278</v>
       </c>
       <c r="V397" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W397" t="s">
         <v>109</v>
       </c>
       <c r="X397" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y397" t="s">
         <v>72</v>
@@ -40791,14 +40791,14 @@
         <v>1278</v>
       </c>
       <c r="V398" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W398" t="s">
         <v>109</v>
       </c>
       <c r="X398" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y398" t="s">
         <v>72</v>
@@ -40869,14 +40869,14 @@
         <v>1278</v>
       </c>
       <c r="V399" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W399" t="s">
         <v>109</v>
       </c>
       <c r="X399" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y399" t="s">
         <v>72</v>
@@ -40947,14 +40947,14 @@
         <v>1278</v>
       </c>
       <c r="V400" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W400" t="s">
         <v>109</v>
       </c>
       <c r="X400" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y400" t="s">
         <v>72</v>
@@ -41025,14 +41025,14 @@
         <v>1278</v>
       </c>
       <c r="V401" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W401" t="s">
         <v>109</v>
       </c>
       <c r="X401" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y401" t="s">
         <v>72</v>
@@ -41103,14 +41103,14 @@
         <v>1278</v>
       </c>
       <c r="V402" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W402" t="s">
         <v>109</v>
       </c>
       <c r="X402" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y402" t="s">
         <v>72</v>
@@ -41181,14 +41181,14 @@
         <v>1278</v>
       </c>
       <c r="V403" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W403" t="s">
         <v>109</v>
       </c>
       <c r="X403" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y403" t="s">
         <v>72</v>
@@ -41259,14 +41259,14 @@
         <v>1278</v>
       </c>
       <c r="V404" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W404" t="s">
         <v>109</v>
       </c>
       <c r="X404" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y404" t="s">
         <v>72</v>
@@ -41337,14 +41337,14 @@
         <v>1278</v>
       </c>
       <c r="V405" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W405" t="s">
         <v>109</v>
       </c>
       <c r="X405" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y405" t="s">
         <v>72</v>
@@ -41415,14 +41415,14 @@
         <v>1278</v>
       </c>
       <c r="V406" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W406" t="s">
         <v>109</v>
       </c>
       <c r="X406" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y406" t="s">
         <v>72</v>
@@ -41493,14 +41493,14 @@
         <v>1278</v>
       </c>
       <c r="V407" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W407" t="s">
         <v>109</v>
       </c>
       <c r="X407" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y407" t="s">
         <v>72</v>
@@ -41571,14 +41571,14 @@
         <v>1278</v>
       </c>
       <c r="V408" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W408" t="s">
         <v>109</v>
       </c>
       <c r="X408" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y408" t="s">
         <v>72</v>
@@ -41649,14 +41649,14 @@
         <v>1278</v>
       </c>
       <c r="V409" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W409" t="s">
         <v>109</v>
       </c>
       <c r="X409" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y409" t="s">
         <v>72</v>
@@ -41727,14 +41727,14 @@
         <v>1278</v>
       </c>
       <c r="V410" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W410" t="s">
         <v>109</v>
       </c>
       <c r="X410" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y410" t="s">
         <v>72</v>
@@ -41805,14 +41805,14 @@
         <v>1278</v>
       </c>
       <c r="V411" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W411" t="s">
         <v>109</v>
       </c>
       <c r="X411" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y411" t="s">
         <v>72</v>
@@ -41883,14 +41883,14 @@
         <v>1278</v>
       </c>
       <c r="V412" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W412" t="s">
         <v>109</v>
       </c>
       <c r="X412" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y412" t="s">
         <v>72</v>
@@ -41961,14 +41961,14 @@
         <v>1278</v>
       </c>
       <c r="V413" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W413" t="s">
         <v>109</v>
       </c>
       <c r="X413" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y413" t="s">
         <v>72</v>
@@ -42039,14 +42039,14 @@
         <v>1278</v>
       </c>
       <c r="V414" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W414" t="s">
         <v>109</v>
       </c>
       <c r="X414" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y414" t="s">
         <v>72</v>
@@ -42117,14 +42117,14 @@
         <v>1278</v>
       </c>
       <c r="V415" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W415" t="s">
         <v>109</v>
       </c>
       <c r="X415" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y415" t="s">
         <v>72</v>
@@ -42195,14 +42195,14 @@
         <v>1278</v>
       </c>
       <c r="V416" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W416" t="s">
         <v>109</v>
       </c>
       <c r="X416" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y416" t="s">
         <v>72</v>
@@ -42273,14 +42273,14 @@
         <v>1278</v>
       </c>
       <c r="V417" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W417" t="s">
         <v>109</v>
       </c>
       <c r="X417" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y417" t="s">
         <v>72</v>
@@ -42351,14 +42351,14 @@
         <v>1278</v>
       </c>
       <c r="V418" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W418" t="s">
         <v>109</v>
       </c>
       <c r="X418" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y418" t="s">
         <v>72</v>
@@ -42429,14 +42429,14 @@
         <v>1278</v>
       </c>
       <c r="V419" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W419" t="s">
         <v>109</v>
       </c>
       <c r="X419" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y419" t="s">
         <v>72</v>
@@ -42507,14 +42507,14 @@
         <v>1278</v>
       </c>
       <c r="V420" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W420" t="s">
         <v>109</v>
       </c>
       <c r="X420" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y420" t="s">
         <v>72</v>
@@ -42585,14 +42585,14 @@
         <v>1278</v>
       </c>
       <c r="V421" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W421" t="s">
         <v>109</v>
       </c>
       <c r="X421" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y421" t="s">
         <v>72</v>
@@ -42663,14 +42663,14 @@
         <v>1278</v>
       </c>
       <c r="V422" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W422" t="s">
         <v>109</v>
       </c>
       <c r="X422" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y422" t="s">
         <v>72</v>
@@ -42741,14 +42741,14 @@
         <v>1278</v>
       </c>
       <c r="V423" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W423" t="s">
         <v>109</v>
       </c>
       <c r="X423" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y423" t="s">
         <v>72</v>
@@ -42819,14 +42819,14 @@
         <v>1278</v>
       </c>
       <c r="V424" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W424" t="s">
         <v>109</v>
       </c>
       <c r="X424" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y424" t="s">
         <v>72</v>
@@ -42897,14 +42897,14 @@
         <v>1278</v>
       </c>
       <c r="V425" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W425" t="s">
         <v>109</v>
       </c>
       <c r="X425" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y425" t="s">
         <v>72</v>
@@ -42975,14 +42975,14 @@
         <v>1278</v>
       </c>
       <c r="V426" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W426" t="s">
         <v>109</v>
       </c>
       <c r="X426" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y426" t="s">
         <v>72</v>
@@ -43053,14 +43053,14 @@
         <v>1278</v>
       </c>
       <c r="V427" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W427" t="s">
         <v>109</v>
       </c>
       <c r="X427" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y427" t="s">
         <v>72</v>
@@ -43131,14 +43131,14 @@
         <v>1278</v>
       </c>
       <c r="V428" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W428" t="s">
         <v>109</v>
       </c>
       <c r="X428" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y428" t="s">
         <v>72</v>
@@ -43209,14 +43209,14 @@
         <v>1278</v>
       </c>
       <c r="V429" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W429" t="s">
         <v>109</v>
       </c>
       <c r="X429" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y429" t="s">
         <v>72</v>
@@ -43287,14 +43287,14 @@
         <v>1278</v>
       </c>
       <c r="V430" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W430" t="s">
         <v>109</v>
       </c>
       <c r="X430" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y430" t="s">
         <v>72</v>
@@ -43365,14 +43365,14 @@
         <v>1278</v>
       </c>
       <c r="V431" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W431" t="s">
         <v>109</v>
       </c>
       <c r="X431" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y431" t="s">
         <v>72</v>
@@ -43443,14 +43443,14 @@
         <v>1278</v>
       </c>
       <c r="V432" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W432" t="s">
         <v>109</v>
       </c>
       <c r="X432" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y432" t="s">
         <v>72</v>
@@ -43521,14 +43521,14 @@
         <v>1278</v>
       </c>
       <c r="V433" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W433" t="s">
         <v>109</v>
       </c>
       <c r="X433" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y433" t="s">
         <v>72</v>
@@ -43599,14 +43599,14 @@
         <v>1278</v>
       </c>
       <c r="V434" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W434" t="s">
         <v>109</v>
       </c>
       <c r="X434" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y434" t="s">
         <v>72</v>
@@ -43677,14 +43677,14 @@
         <v>1278</v>
       </c>
       <c r="V435" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W435" t="s">
         <v>109</v>
       </c>
       <c r="X435" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y435" t="s">
         <v>72</v>
@@ -43755,14 +43755,14 @@
         <v>1278</v>
       </c>
       <c r="V436" t="s">
-        <v>1278</v>
+        <v>2368</v>
       </c>
       <c r="W436" t="s">
         <v>109</v>
       </c>
       <c r="X436" t="str">
         <f t="shared" si="6"/>
-        <v>Itr_B</v>
+        <v>Itn_B</v>
       </c>
       <c r="Y436" t="s">
         <v>72</v>
